--- a/artfynd/A 35211-2025 artfynd.xlsx
+++ b/artfynd/A 35211-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103417634</v>
+        <v>103417628</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,17 +703,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Furuviken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481622.903073605</v>
+        <v>481570</v>
       </c>
       <c r="R2" t="n">
-        <v>6974933.437919989</v>
+        <v>6974870</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,27 +755,18 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103417628</v>
+        <v>103417630</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481570.0448539853</v>
+        <v>481601</v>
       </c>
       <c r="R3" t="n">
-        <v>6974869.910614693</v>
+        <v>6974916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +865,9 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103417630</v>
+        <v>103417631</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,29 +923,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Furuviken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481601.3496791327</v>
+        <v>481603</v>
       </c>
       <c r="R4" t="n">
-        <v>6974916.235363411</v>
+        <v>6974916</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,28 +963,17 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1040,12 +995,7 @@
         <v>103417632</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481615.062973601</v>
+        <v>481615</v>
       </c>
       <c r="R5" t="n">
-        <v>6974919.349470445</v>
+        <v>6974919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,19 +1060,9 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,15 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103417631</v>
+        <v>103417633</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,17 +1117,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Furuviken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>481603.1757266673</v>
+        <v>481623</v>
       </c>
       <c r="R6" t="n">
-        <v>6974916.225091735</v>
+        <v>6974933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,27 +1169,18 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1196,213 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103417635</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Furuviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>481621</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6974940</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103417636</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Furuviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>481613</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6974947</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hackås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35211-2025 artfynd.xlsx
+++ b/artfynd/A 35211-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417628</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417630</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417631</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417632</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417633</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417635</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,8 +1438,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103417636</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>